--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="160">
   <si>
     <t>Mat</t>
   </si>
@@ -100,6 +100,9 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
     <t>PAZ</t>
   </si>
   <si>
@@ -232,6 +235,9 @@
     <t>TORRES</t>
   </si>
   <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
     <t>FIGUEROA</t>
   </si>
   <si>
@@ -328,6 +334,9 @@
     <t>VALERIA</t>
   </si>
   <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
     <t>XIMENA ANALY</t>
   </si>
   <si>
@@ -457,7 +466,7 @@
     <t>HEIDI</t>
   </si>
   <si>
-    <t>HELI AIMME</t>
+    <t>HELI AIMEE</t>
   </si>
   <si>
     <t>PAOLA</t>
@@ -937,19 +946,19 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>14</v>
       </c>
       <c r="G4">
-        <v>41.18</v>
+        <v>40</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -963,7 +972,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -972,13 +981,13 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>88.23999999999999</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -989,7 +998,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -998,10 +1007,10 @@
         <v>21</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>46.15</v>
+        <v>47.5</v>
       </c>
       <c r="H6">
         <v>5.9</v>
@@ -1172,13 +1181,13 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1195,13 +1204,13 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1218,13 +1227,13 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1398,19 +1407,19 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>14</v>
       </c>
       <c r="G4">
-        <v>41.18</v>
+        <v>40</v>
       </c>
       <c r="H4">
         <v>6.1</v>
@@ -1424,7 +1433,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1433,13 +1442,13 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>88.23999999999999</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1450,7 +1459,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1459,10 +1468,10 @@
         <v>21</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>46.15</v>
+        <v>47.5</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -1547,7 +1556,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1585,10 +1594,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1608,10 +1617,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1631,10 +1640,10 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1654,10 +1663,10 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1671,16 +1680,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920067</v>
+        <v>23330051920213</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1694,16 +1703,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920071</v>
+        <v>23330051920067</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1717,16 +1726,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920072</v>
+        <v>23330051920071</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1740,16 +1749,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920074</v>
+        <v>23330051920072</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1763,22 +1772,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920082</v>
+        <v>23330051920074</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1786,16 +1795,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920083</v>
+        <v>23330051920082</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1809,16 +1818,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920091</v>
+        <v>23330051920083</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1832,16 +1841,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920097</v>
+        <v>23330051920091</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1855,16 +1864,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920105</v>
+        <v>23330051920097</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1878,16 +1887,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920112</v>
+        <v>23330051920105</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1901,22 +1910,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920133</v>
+        <v>23330051920112</v>
       </c>
       <c r="B16" t="s">
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1924,16 +1933,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920255</v>
+        <v>23330051920133</v>
       </c>
       <c r="B17" t="s">
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1947,16 +1956,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920315</v>
+        <v>23330051920255</v>
       </c>
       <c r="B18" t="s">
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1970,16 +1979,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920146</v>
+        <v>23330051920315</v>
       </c>
       <c r="B19" t="s">
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1993,22 +2002,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920157</v>
+        <v>23330051920146</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -2016,16 +2025,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920158</v>
+        <v>23330051920157</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -2039,16 +2048,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920159</v>
+        <v>23330051920158</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -2062,16 +2071,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920167</v>
+        <v>23330051920159</v>
       </c>
       <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
         <v>41</v>
       </c>
-      <c r="C23" t="s">
-        <v>28</v>
-      </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -2085,16 +2094,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920171</v>
+        <v>23330051920167</v>
       </c>
       <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
         <v>29</v>
       </c>
-      <c r="C24" t="s">
-        <v>33</v>
-      </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -2108,39 +2117,39 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920005</v>
+        <v>23330051920171</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920008</v>
+        <v>23330051920005</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2154,16 +2163,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920009</v>
+        <v>23330051920008</v>
       </c>
       <c r="B27" t="s">
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2177,16 +2186,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920016</v>
+        <v>23330051920009</v>
       </c>
       <c r="B28" t="s">
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2200,16 +2209,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920021</v>
+        <v>23330051920016</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2223,16 +2232,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920020</v>
+        <v>23330051920021</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2246,22 +2255,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920035</v>
+        <v>23330051920020</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2269,16 +2278,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920037</v>
+        <v>23330051920035</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2292,22 +2301,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920057</v>
+        <v>23330051920037</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="D33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2315,16 +2324,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920246</v>
+        <v>23330051920057</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="D34" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2338,16 +2347,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920061</v>
+        <v>23330051920246</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D35" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2361,16 +2370,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920062</v>
+        <v>23330051920061</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C36" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="D36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2384,16 +2393,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920064</v>
+        <v>23330051920062</v>
       </c>
       <c r="B37" t="s">
         <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D37" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2407,16 +2416,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>23330051920259</v>
+        <v>23330051920064</v>
       </c>
       <c r="B38" t="s">
         <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="D38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2430,16 +2439,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>23330051920065</v>
+        <v>23330051920259</v>
       </c>
       <c r="B39" t="s">
         <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D39" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2453,16 +2462,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>23330051920066</v>
+        <v>23330051920065</v>
       </c>
       <c r="B40" t="s">
         <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2476,22 +2485,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>23330051920077</v>
+        <v>23330051920066</v>
       </c>
       <c r="B41" t="s">
         <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D41" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2499,16 +2508,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>23330051920081</v>
+        <v>23330051920077</v>
       </c>
       <c r="B42" t="s">
         <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D42" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2522,16 +2531,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>23330051920086</v>
+        <v>23330051920081</v>
       </c>
       <c r="B43" t="s">
         <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D43" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2545,16 +2554,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>23330051920084</v>
+        <v>23330051920086</v>
       </c>
       <c r="B44" t="s">
         <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="D44" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2568,16 +2577,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>23330051920090</v>
+        <v>23330051920084</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C45" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="D45" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2591,16 +2600,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>23330051920102</v>
+        <v>23330051920090</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="D46" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2614,16 +2623,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>23330051920103</v>
+        <v>23330051920102</v>
       </c>
       <c r="B47" t="s">
         <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D47" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2637,16 +2646,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>23330051920104</v>
+        <v>23330051920103</v>
       </c>
       <c r="B48" t="s">
         <v>59</v>
       </c>
       <c r="C48" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="D48" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2660,16 +2669,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>23330051920107</v>
+        <v>23330051920104</v>
       </c>
       <c r="B49" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C49" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="D49" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2683,16 +2692,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>23330051920110</v>
+        <v>23330051920107</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C50" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -2706,22 +2715,22 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>23330051920119</v>
+        <v>23330051920110</v>
       </c>
       <c r="B51" t="s">
         <v>61</v>
       </c>
       <c r="C51" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="D51" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -2729,16 +2738,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>23330051920121</v>
+        <v>23330051920119</v>
       </c>
       <c r="B52" t="s">
         <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D52" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2752,16 +2761,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>23330051920127</v>
+        <v>23330051920121</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="C53" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D53" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -2775,16 +2784,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>23330051920134</v>
+        <v>23330051920127</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C54" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D54" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -2798,16 +2807,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>23330051920141</v>
+        <v>23330051920134</v>
       </c>
       <c r="B55" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="D55" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -2821,16 +2830,16 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>23330051920142</v>
+        <v>23330051920141</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C56" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D56" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -2844,16 +2853,16 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>23330051920143</v>
+        <v>23330051920142</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="C57" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="D57" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -2867,16 +2876,16 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>23330051920144</v>
+        <v>23330051920143</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C58" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="D58" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -2890,16 +2899,16 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>23330051920145</v>
+        <v>23330051920144</v>
       </c>
       <c r="B59" t="s">
         <v>65</v>
       </c>
       <c r="C59" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D59" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -2913,16 +2922,16 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>23330051920149</v>
+        <v>23330051920145</v>
       </c>
       <c r="B60" t="s">
         <v>66</v>
       </c>
       <c r="C60" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="D60" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -2936,16 +2945,16 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>23330051920150</v>
+        <v>23330051920149</v>
       </c>
       <c r="B61" t="s">
         <v>67</v>
       </c>
       <c r="C61" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D61" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -2954,6 +2963,29 @@
         <v>15</v>
       </c>
       <c r="G61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62">
+        <v>23330051920150</v>
+      </c>
+      <c r="B62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" t="s">
+        <v>59</v>
+      </c>
+      <c r="D62" t="s">
+        <v>159</v>
+      </c>
+      <c r="E62" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="141">
   <si>
     <t>Mat</t>
   </si>
@@ -88,31 +88,76 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MONTERD</t>
-  </si>
-  <si>
-    <t>TELLO</t>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ALCANTARA</t>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
   </si>
   <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>SOSA</t>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>AZPIRI</t>
   </si>
   <si>
     <t>CASTILLO</t>
@@ -121,18 +166,18 @@
     <t>COCOTLE</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>RICO</t>
   </si>
   <si>
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
@@ -142,361 +187,259 @@
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>UTRERA</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>CALCANEO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VARILLAS</t>
+  </si>
+  <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>CARPINTEYRO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSA</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>ARCOS</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>MANZANO</t>
   </si>
   <si>
     <t>MONTIEL</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>TENORIO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
-    <t>CARPINTEYRO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TZNAHUA</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
-  </si>
-  <si>
-    <t>MANZANO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>POOT</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>VARILLAS</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>SALINAS</t>
-  </si>
-  <si>
-    <t>JUAN YAHEL</t>
-  </si>
-  <si>
-    <t>ANGEL YAMIL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
+    <t>CORREA</t>
+  </si>
+  <si>
+    <t>CARLOS DAVID</t>
+  </si>
+  <si>
+    <t>IAN</t>
+  </si>
+  <si>
+    <t>ROMINA GISELLE</t>
+  </si>
+  <si>
+    <t>MELANY</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>DIANA ARLET</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>ESTRELLA ESMERALDA</t>
+  </si>
+  <si>
+    <t>ESTRELLA RUBI</t>
+  </si>
+  <si>
+    <t>KENYA MARIANA</t>
+  </si>
+  <si>
+    <t>LEONARDO GABRIEL</t>
+  </si>
+  <si>
+    <t>OMAR DAVID</t>
+  </si>
+  <si>
+    <t>JUAN SEBASTIAN</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>LEONEL</t>
+  </si>
+  <si>
+    <t>JAZIEL</t>
+  </si>
+  <si>
+    <t>YAELIS</t>
+  </si>
+  <si>
+    <t>LLUVIA ITZEL</t>
+  </si>
+  <si>
+    <t>DENISSE</t>
+  </si>
+  <si>
+    <t>XIMENA ANALY</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
   </si>
   <si>
     <t>VALERIA</t>
   </si>
   <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>XIMENA ANALY</t>
-  </si>
-  <si>
-    <t>IVONNE ERIMAR</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>MARIEL BIDEMI</t>
-  </si>
-  <si>
     <t>MARIA GUADALUPE</t>
   </si>
   <si>
+    <t>JANETH</t>
+  </si>
+  <si>
+    <t>ILSE JIMENA</t>
+  </si>
+  <si>
     <t>VIRIDIANA</t>
   </si>
   <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>MELANY</t>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>MARGARITA</t>
   </si>
   <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>TATIANA</t>
+  </si>
+  <si>
     <t>DANIA LIZETH</t>
   </si>
   <si>
+    <t>KENIA PAOLA</t>
+  </si>
+  <si>
     <t>CINTHIA</t>
   </si>
   <si>
+    <t>MARYGELLI</t>
+  </si>
+  <si>
     <t>ANGEL URIEL</t>
   </si>
   <si>
+    <t>KAREN AMERICA</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>MAGALY</t>
+  </si>
+  <si>
     <t>LEYLA SARAI</t>
   </si>
   <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
     <t>JAIR</t>
   </si>
   <si>
     <t>DORIAN ALEXANDER</t>
   </si>
   <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
     <t>SALMA JANET</t>
   </si>
   <si>
+    <t>ELIUD EDUARDO</t>
+  </si>
+  <si>
+    <t>KAORY AYELEN</t>
+  </si>
+  <si>
     <t>JONATHAN ISAI</t>
-  </si>
-  <si>
-    <t>OMAR DAVID</t>
-  </si>
-  <si>
-    <t>JUAN SEBASTIAN</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>HERSON</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
-  </si>
-  <si>
-    <t>CRIZULY AMITHAI</t>
-  </si>
-  <si>
-    <t>LLUVIA ITZEL</t>
-  </si>
-  <si>
-    <t>REINA IVETT</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>KAROL BALAAM</t>
-  </si>
-  <si>
-    <t>MELANIE YARETZI</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>YASMIN</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>JANETH</t>
-  </si>
-  <si>
-    <t>ILSE JIMENA</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>REY</t>
-  </si>
-  <si>
-    <t>ARELI DANAE</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>HEIDI</t>
-  </si>
-  <si>
-    <t>HELI AIMEE</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>KENIA PAOLA</t>
-  </si>
-  <si>
-    <t>MARYGELLI</t>
-  </si>
-  <si>
-    <t>KAREN AMERICA</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>MAGALY</t>
-  </si>
-  <si>
-    <t>VERONICA</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
   </si>
 </sst>
 </file>
@@ -946,19 +889,19 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>14</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>41.18</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -972,7 +915,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -981,13 +924,13 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>88.56999999999999</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1138,16 +1081,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>37.04</v>
+      </c>
+      <c r="H2">
+        <v>5.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1161,16 +1107,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>41.67</v>
+      </c>
+      <c r="H3">
+        <v>5.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1181,19 +1130,22 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>61.76</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1204,13 +1156,13 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1230,16 +1182,19 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>57.5</v>
+      </c>
+      <c r="H6">
+        <v>5.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1273,16 +1228,19 @@
         <v>39</v>
       </c>
       <c r="D8">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>46.15</v>
+      </c>
+      <c r="H8">
+        <v>5.9</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1296,16 +1254,19 @@
         <v>30</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>36.67</v>
+      </c>
+      <c r="H9">
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>
@@ -1361,16 +1322,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>44.44</v>
+        <v>37.04</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1387,16 +1348,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>37.5</v>
+        <v>41.67</v>
       </c>
       <c r="H3">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1407,22 +1368,22 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
+        <v>13</v>
+      </c>
+      <c r="F4">
         <v>21</v>
       </c>
-      <c r="F4">
-        <v>14</v>
-      </c>
       <c r="G4">
-        <v>40</v>
+        <v>61.76</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1433,7 +1394,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1442,13 +1403,13 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>88.56999999999999</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1465,16 +1426,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>47.5</v>
+        <v>57.5</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1511,16 +1472,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G8">
-        <v>38.46</v>
+        <v>46.15</v>
       </c>
       <c r="H8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1537,16 +1498,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>30</v>
+        <v>36.67</v>
       </c>
       <c r="H9">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -1556,7 +1517,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1588,16 +1549,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920015</v>
+        <v>23330051920018</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1611,22 +1572,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920017</v>
+        <v>23330051920043</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1634,22 +1595,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920022</v>
+        <v>23330051920095</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1657,22 +1618,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920038</v>
+        <v>23330051920105</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1680,22 +1641,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920213</v>
+        <v>23330051920118</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1703,22 +1664,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920067</v>
+        <v>23330051920123</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1726,22 +1687,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920071</v>
+        <v>23330051920139</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1749,22 +1710,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920072</v>
+        <v>23330051920155</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1772,22 +1733,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920074</v>
+        <v>23330051920154</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1795,22 +1756,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920082</v>
+        <v>23330051920165</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1818,22 +1779,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920083</v>
+        <v>23330051920166</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1841,321 +1802,321 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920091</v>
+        <v>23330051920005</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920097</v>
+        <v>23330051920008</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920105</v>
+        <v>23330051920009</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920112</v>
+        <v>23330051920021</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920133</v>
+        <v>23330051920020</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920255</v>
+        <v>23330051920035</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920315</v>
+        <v>23330051920037</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920146</v>
+        <v>23330051920039</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920157</v>
+        <v>23330051920049</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920158</v>
+        <v>23330051920246</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920159</v>
+        <v>23330051920065</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920167</v>
+        <v>23330051920067</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920171</v>
+        <v>23330051920072</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920005</v>
+        <v>23330051920077</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2163,22 +2124,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920008</v>
+        <v>23330051920079</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2186,22 +2147,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920009</v>
+        <v>23330051920082</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2209,22 +2170,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920016</v>
+        <v>23330051920083</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2232,22 +2193,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920021</v>
+        <v>23330051920086</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2255,22 +2216,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920020</v>
+        <v>23330051920084</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2278,22 +2239,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920035</v>
+        <v>23330051920091</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2301,22 +2262,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920037</v>
+        <v>23330051920104</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2324,22 +2285,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920057</v>
+        <v>23330051920112</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2347,22 +2308,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920246</v>
+        <v>23330051920121</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2370,22 +2331,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920061</v>
+        <v>23330051920130</v>
       </c>
       <c r="B36" t="s">
         <v>38</v>
       </c>
       <c r="C36" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2393,22 +2354,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920062</v>
+        <v>23330051920133</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D37" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2416,22 +2377,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>23330051920064</v>
+        <v>23330051920134</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D38" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2439,22 +2400,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>23330051920259</v>
+        <v>23330051920255</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D39" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2462,22 +2423,22 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>23330051920065</v>
+        <v>23330051920141</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2485,22 +2446,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>23330051920066</v>
+        <v>23330051920315</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D41" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2508,22 +2469,22 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>23330051920077</v>
+        <v>23330051920142</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2531,22 +2492,22 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>23330051920081</v>
+        <v>23330051920144</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C43" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="D43" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2554,22 +2515,22 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>23330051920086</v>
+        <v>23330051920145</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C44" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="D44" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2577,22 +2538,22 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>23330051920084</v>
+        <v>23330051920146</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C45" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="D45" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2600,22 +2561,22 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>23330051920090</v>
+        <v>23330051920150</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C46" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="D46" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2623,22 +2584,22 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>23330051920102</v>
+        <v>23330051920157</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C47" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D47" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2646,22 +2607,22 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>23330051920103</v>
+        <v>23330051920158</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C48" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="D48" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2669,22 +2630,22 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>23330051920104</v>
+        <v>23330051920167</v>
       </c>
       <c r="B49" t="s">
         <v>60</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="D49" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -2692,22 +2653,22 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>23330051920107</v>
+        <v>23330051920354</v>
       </c>
       <c r="B50" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="D50" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -2715,22 +2676,22 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>23330051920110</v>
+        <v>23330051920170</v>
       </c>
       <c r="B51" t="s">
         <v>61</v>
       </c>
       <c r="C51" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="D51" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -2738,254 +2699,24 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>23330051920119</v>
+        <v>23330051920171</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C52" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="D52" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>23330051920121</v>
-      </c>
-      <c r="B53" t="s">
-        <v>63</v>
-      </c>
-      <c r="C53" t="s">
-        <v>96</v>
-      </c>
-      <c r="D53" t="s">
-        <v>150</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>15</v>
-      </c>
-      <c r="G53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54">
-        <v>23330051920127</v>
-      </c>
-      <c r="B54" t="s">
-        <v>34</v>
-      </c>
-      <c r="C54" t="s">
-        <v>97</v>
-      </c>
-      <c r="D54" t="s">
-        <v>151</v>
-      </c>
-      <c r="E54" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>15</v>
-      </c>
-      <c r="G54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55">
-        <v>23330051920134</v>
-      </c>
-      <c r="B55" t="s">
-        <v>26</v>
-      </c>
-      <c r="C55" t="s">
-        <v>34</v>
-      </c>
-      <c r="D55" t="s">
-        <v>152</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" t="s">
-        <v>15</v>
-      </c>
-      <c r="G55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56">
-        <v>23330051920141</v>
-      </c>
-      <c r="B56" t="s">
-        <v>52</v>
-      </c>
-      <c r="C56" t="s">
-        <v>98</v>
-      </c>
-      <c r="D56" t="s">
-        <v>153</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" t="s">
-        <v>15</v>
-      </c>
-      <c r="G56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57">
-        <v>23330051920142</v>
-      </c>
-      <c r="B57" t="s">
-        <v>64</v>
-      </c>
-      <c r="C57" t="s">
-        <v>54</v>
-      </c>
-      <c r="D57" t="s">
-        <v>154</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>15</v>
-      </c>
-      <c r="G57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58">
-        <v>23330051920143</v>
-      </c>
-      <c r="B58" t="s">
-        <v>29</v>
-      </c>
-      <c r="C58" t="s">
-        <v>99</v>
-      </c>
-      <c r="D58" t="s">
-        <v>155</v>
-      </c>
-      <c r="E58" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" t="s">
-        <v>15</v>
-      </c>
-      <c r="G58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59">
-        <v>23330051920144</v>
-      </c>
-      <c r="B59" t="s">
-        <v>65</v>
-      </c>
-      <c r="C59" t="s">
-        <v>65</v>
-      </c>
-      <c r="D59" t="s">
-        <v>156</v>
-      </c>
-      <c r="E59" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" t="s">
-        <v>15</v>
-      </c>
-      <c r="G59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60">
-        <v>23330051920145</v>
-      </c>
-      <c r="B60" t="s">
-        <v>66</v>
-      </c>
-      <c r="C60" t="s">
-        <v>41</v>
-      </c>
-      <c r="D60" t="s">
-        <v>157</v>
-      </c>
-      <c r="E60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" t="s">
-        <v>15</v>
-      </c>
-      <c r="G60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61">
-        <v>23330051920149</v>
-      </c>
-      <c r="B61" t="s">
-        <v>67</v>
-      </c>
-      <c r="C61" t="s">
-        <v>100</v>
-      </c>
-      <c r="D61" t="s">
-        <v>158</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>15</v>
-      </c>
-      <c r="G61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62">
-        <v>23330051920150</v>
-      </c>
-      <c r="B62" t="s">
-        <v>68</v>
-      </c>
-      <c r="C62" t="s">
-        <v>59</v>
-      </c>
-      <c r="D62" t="s">
-        <v>159</v>
-      </c>
-      <c r="E62" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" t="s">
-        <v>15</v>
-      </c>
-      <c r="G62">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="143">
   <si>
     <t>Mat</t>
   </si>
@@ -112,93 +112,93 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>AZPIRI</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>MELO</t>
   </si>
   <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>ARENAS</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>AZPIRI</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
@@ -223,66 +223,69 @@
     <t>NIEVES</t>
   </si>
   <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>CALCANEO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VARILLAS</t>
+  </si>
+  <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>CARPINTEYRO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSA</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>ARCOS</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>MANZANO</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>CALCANEO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>VARILLAS</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>CARPINTEYRO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSA</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>MANZANO</t>
-  </si>
-  <si>
     <t>MONTIEL</t>
   </si>
   <si>
@@ -316,120 +319,126 @@
     <t>ESTRELLA RUBI</t>
   </si>
   <si>
+    <t>LEONARDO GABRIEL</t>
+  </si>
+  <si>
+    <t>VICTOR JESUS</t>
+  </si>
+  <si>
+    <t>JONATHAN ISAI</t>
+  </si>
+  <si>
+    <t>OMAR DAVID</t>
+  </si>
+  <si>
+    <t>JUAN SEBASTIAN</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>LEONEL</t>
+  </si>
+  <si>
+    <t>JAZIEL</t>
+  </si>
+  <si>
+    <t>YAELIS</t>
+  </si>
+  <si>
+    <t>LLUVIA ITZEL</t>
+  </si>
+  <si>
+    <t>DENISSE</t>
+  </si>
+  <si>
+    <t>XIMENA ANALY</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>JANETH</t>
+  </si>
+  <si>
+    <t>ILSE JIMENA</t>
+  </si>
+  <si>
+    <t>VIRIDIANA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MARGARITA</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>TATIANA</t>
+  </si>
+  <si>
+    <t>DANIA LIZETH</t>
+  </si>
+  <si>
+    <t>KENIA PAOLA</t>
+  </si>
+  <si>
+    <t>CINTHIA</t>
+  </si>
+  <si>
+    <t>MARYGELLI</t>
+  </si>
+  <si>
+    <t>ANGEL URIEL</t>
+  </si>
+  <si>
+    <t>KAREN AMERICA</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>MAGALY</t>
+  </si>
+  <si>
+    <t>LEYLA SARAI</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>DORIAN ALEXANDER</t>
+  </si>
+  <si>
     <t>KENYA MARIANA</t>
   </si>
   <si>
-    <t>LEONARDO GABRIEL</t>
-  </si>
-  <si>
-    <t>OMAR DAVID</t>
-  </si>
-  <si>
-    <t>JUAN SEBASTIAN</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
-  </si>
-  <si>
-    <t>JAZIEL</t>
-  </si>
-  <si>
-    <t>YAELIS</t>
-  </si>
-  <si>
-    <t>LLUVIA ITZEL</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>XIMENA ANALY</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>JANETH</t>
-  </si>
-  <si>
-    <t>ILSE JIMENA</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MARGARITA</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>TATIANA</t>
-  </si>
-  <si>
-    <t>DANIA LIZETH</t>
-  </si>
-  <si>
-    <t>KENIA PAOLA</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>MARYGELLI</t>
-  </si>
-  <si>
-    <t>ANGEL URIEL</t>
-  </si>
-  <si>
-    <t>KAREN AMERICA</t>
-  </si>
-  <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>MAGALY</t>
-  </si>
-  <si>
-    <t>LEYLA SARAI</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>DORIAN ALEXANDER</t>
-  </si>
-  <si>
     <t>SALMA JANET</t>
   </si>
   <si>
@@ -437,9 +446,6 @@
   </si>
   <si>
     <t>KAORY AYELEN</t>
-  </si>
-  <si>
-    <t>JONATHAN ISAI</t>
   </si>
 </sst>
 </file>
@@ -1517,7 +1523,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1558,7 +1564,7 @@
         <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1581,7 +1587,7 @@
         <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1604,7 +1610,7 @@
         <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1627,7 +1633,7 @@
         <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1650,7 +1656,7 @@
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1673,7 +1679,7 @@
         <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1696,7 +1702,7 @@
         <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1719,7 +1725,7 @@
         <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1742,7 +1748,7 @@
         <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1756,16 +1762,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920165</v>
+        <v>23330051920166</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1779,16 +1785,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920166</v>
+        <v>23330051920169</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1802,39 +1808,39 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920005</v>
+        <v>23330051920171</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920008</v>
+        <v>23330051920005</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1848,16 +1854,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920009</v>
+        <v>23330051920008</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1871,16 +1877,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920021</v>
+        <v>23330051920009</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1894,16 +1900,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920020</v>
+        <v>23330051920021</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1917,22 +1923,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920035</v>
+        <v>23330051920020</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1940,16 +1946,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920037</v>
+        <v>23330051920035</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1963,16 +1969,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920039</v>
+        <v>23330051920037</v>
       </c>
       <c r="B20" t="s">
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1986,22 +1992,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920049</v>
+        <v>23330051920039</v>
       </c>
       <c r="B21" t="s">
         <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -2009,16 +2015,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920246</v>
+        <v>23330051920049</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -2032,16 +2038,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920065</v>
+        <v>23330051920246</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="D23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -2055,16 +2061,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920067</v>
+        <v>23330051920065</v>
       </c>
       <c r="B24" t="s">
         <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -2078,16 +2084,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920072</v>
+        <v>23330051920067</v>
       </c>
       <c r="B25" t="s">
         <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2101,22 +2107,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920077</v>
+        <v>23330051920072</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2124,16 +2130,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920079</v>
+        <v>23330051920077</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2147,16 +2153,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920082</v>
+        <v>23330051920079</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2170,16 +2176,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920083</v>
+        <v>23330051920082</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2193,16 +2199,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920086</v>
+        <v>23330051920083</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2216,16 +2222,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920084</v>
+        <v>23330051920086</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2239,16 +2245,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920091</v>
+        <v>23330051920084</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2262,16 +2268,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920104</v>
+        <v>23330051920091</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2285,16 +2291,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920112</v>
+        <v>23330051920104</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2308,22 +2314,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920121</v>
+        <v>23330051920112</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2331,16 +2337,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920130</v>
+        <v>23330051920121</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2354,16 +2360,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920133</v>
+        <v>23330051920130</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2377,16 +2383,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>23330051920134</v>
+        <v>23330051920133</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2400,16 +2406,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>23330051920255</v>
+        <v>23330051920134</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2423,16 +2429,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>23330051920141</v>
+        <v>23330051920255</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D40" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2446,16 +2452,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>23330051920315</v>
+        <v>23330051920141</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D41" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2469,16 +2475,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>23330051920142</v>
+        <v>23330051920315</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="D42" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2492,16 +2498,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>23330051920144</v>
+        <v>23330051920142</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D43" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2515,16 +2521,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>23330051920145</v>
+        <v>23330051920144</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D44" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2538,16 +2544,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>23330051920146</v>
+        <v>23330051920145</v>
       </c>
       <c r="B45" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C45" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="D45" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2561,16 +2567,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>23330051920150</v>
+        <v>23330051920146</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C46" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D46" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2584,22 +2590,22 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>23330051920157</v>
+        <v>23330051920150</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="D47" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2607,16 +2613,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>23330051920158</v>
+        <v>23330051920157</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C48" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D48" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2630,16 +2636,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>23330051920167</v>
+        <v>23330051920158</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C49" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D49" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2653,16 +2659,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>23330051920354</v>
+        <v>23330051920165</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
         <v>88</v>
       </c>
       <c r="D50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -2676,16 +2682,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>23330051920170</v>
+        <v>23330051920167</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="D51" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2699,16 +2705,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>23330051920171</v>
+        <v>23330051920354</v>
       </c>
       <c r="B52" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C52" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="D52" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2717,6 +2723,29 @@
         <v>16</v>
       </c>
       <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>23330051920170</v>
+      </c>
+      <c r="B53" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" t="s">
+        <v>90</v>
+      </c>
+      <c r="D53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="145">
   <si>
     <t>Mat</t>
   </si>
@@ -94,6 +94,9 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
@@ -175,9 +178,6 @@
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
@@ -211,6 +211,9 @@
     <t>SOLANO</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -296,6 +299,9 @@
   </si>
   <si>
     <t>IAN</t>
+  </si>
+  <si>
+    <t>HUGO ISAI</t>
   </si>
   <si>
     <t>ROMINA GISELLE</t>
@@ -1165,16 +1171,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>91.18000000000001</v>
+      </c>
+      <c r="H5">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1406,16 +1415,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>88.23999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1523,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1564,7 +1573,7 @@
         <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1587,7 +1596,7 @@
         <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1601,7 +1610,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920095</v>
+        <v>23330051920052</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
@@ -1610,13 +1619,13 @@
         <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1624,7 +1633,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920105</v>
+        <v>23330051920095</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -1633,7 +1642,7 @@
         <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1647,22 +1656,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920118</v>
+        <v>23330051920105</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1670,16 +1679,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920123</v>
+        <v>23330051920118</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1693,16 +1702,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920139</v>
+        <v>23330051920123</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1716,22 +1725,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920155</v>
+        <v>23330051920139</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1739,16 +1748,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920154</v>
+        <v>23330051920155</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1762,16 +1771,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920166</v>
+        <v>23330051920154</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1785,16 +1794,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920169</v>
+        <v>23330051920166</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1808,16 +1817,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920171</v>
+        <v>23330051920169</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1831,39 +1840,39 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920005</v>
+        <v>23330051920171</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920008</v>
+        <v>23330051920005</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1877,16 +1886,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920009</v>
+        <v>23330051920008</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1900,16 +1909,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920021</v>
+        <v>23330051920009</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1923,16 +1932,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920020</v>
+        <v>23330051920021</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1946,22 +1955,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920035</v>
+        <v>23330051920020</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1969,16 +1978,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920037</v>
+        <v>23330051920035</v>
       </c>
       <c r="B20" t="s">
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1992,7 +2001,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920039</v>
+        <v>23330051920037</v>
       </c>
       <c r="B21" t="s">
         <v>41</v>
@@ -2001,7 +2010,7 @@
         <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -2015,7 +2024,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920049</v>
+        <v>23330051920039</v>
       </c>
       <c r="B22" t="s">
         <v>42</v>
@@ -2024,13 +2033,13 @@
         <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -2038,16 +2047,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920246</v>
+        <v>23330051920049</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
         <v>74</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -2061,16 +2070,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920065</v>
+        <v>23330051920246</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -2084,16 +2093,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920067</v>
+        <v>23330051920065</v>
       </c>
       <c r="B25" t="s">
         <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2107,16 +2116,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920072</v>
+        <v>23330051920067</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2130,22 +2139,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920077</v>
+        <v>23330051920072</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
         <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2153,7 +2162,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920079</v>
+        <v>23330051920077</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
@@ -2162,7 +2171,7 @@
         <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2176,7 +2185,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920082</v>
+        <v>23330051920079</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
@@ -2185,7 +2194,7 @@
         <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2199,16 +2208,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920083</v>
+        <v>23330051920082</v>
       </c>
       <c r="B30" t="s">
         <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2222,16 +2231,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920086</v>
+        <v>23330051920083</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2245,16 +2254,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920084</v>
+        <v>23330051920086</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2268,16 +2277,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920091</v>
+        <v>23330051920084</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="D33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2291,16 +2300,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920104</v>
+        <v>23330051920091</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
         <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2314,7 +2323,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920112</v>
+        <v>23330051920104</v>
       </c>
       <c r="B35" t="s">
         <v>51</v>
@@ -2323,7 +2332,7 @@
         <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2337,7 +2346,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920121</v>
+        <v>23330051920112</v>
       </c>
       <c r="B36" t="s">
         <v>52</v>
@@ -2346,13 +2355,13 @@
         <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2360,16 +2369,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920130</v>
+        <v>23330051920121</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
         <v>84</v>
       </c>
       <c r="D37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2383,16 +2392,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>23330051920133</v>
+        <v>23330051920130</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="D38" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2406,16 +2415,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>23330051920134</v>
+        <v>23330051920133</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2429,16 +2438,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>23330051920255</v>
+        <v>23330051920134</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2452,16 +2461,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>23330051920141</v>
+        <v>23330051920255</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
         <v>86</v>
       </c>
       <c r="D41" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2475,16 +2484,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>23330051920315</v>
+        <v>23330051920141</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C42" t="s">
         <v>87</v>
       </c>
       <c r="D42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2498,16 +2507,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>23330051920142</v>
+        <v>23330051920315</v>
       </c>
       <c r="B43" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="D43" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2521,16 +2530,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>23330051920144</v>
+        <v>23330051920142</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2544,16 +2553,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>23330051920145</v>
+        <v>23330051920144</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D45" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2567,16 +2576,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>23330051920146</v>
+        <v>23330051920145</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C46" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="D46" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2590,16 +2599,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>23330051920150</v>
+        <v>23330051920146</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D47" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2613,22 +2622,22 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>23330051920157</v>
+        <v>23330051920150</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="D48" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2636,16 +2645,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>23330051920158</v>
+        <v>23330051920157</v>
       </c>
       <c r="B49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C49" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D49" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2659,16 +2668,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>23330051920165</v>
+        <v>23330051920158</v>
       </c>
       <c r="B50" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C50" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="D50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -2682,16 +2691,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>23330051920167</v>
+        <v>23330051920165</v>
       </c>
       <c r="B51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C51" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="D51" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2705,16 +2714,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>23330051920354</v>
+        <v>23330051920167</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="D52" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2728,16 +2737,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>23330051920170</v>
+        <v>23330051920354</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="C53" t="s">
         <v>90</v>
       </c>
       <c r="D53" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -2746,6 +2755,29 @@
         <v>16</v>
       </c>
       <c r="G53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>23330051920170</v>
+      </c>
+      <c r="B54" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" t="s">
+        <v>91</v>
+      </c>
+      <c r="D54" t="s">
+        <v>144</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="124">
   <si>
     <t>Mat</t>
   </si>
@@ -88,370 +88,307 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>RAMOS</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MONTERD</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>VELUETA</t>
+  </si>
+  <si>
+    <t>VIVANCO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TELLO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>CERON</t>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>AZPIRI</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CALCANEO</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>ARENAS</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
   </si>
   <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>AZPIRI</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>UTRERA</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
+    <t>MANZANO</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
   </si>
   <si>
     <t>COXCAHUA</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>CALCANEO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>VARILLAS</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>CARPINTEYRO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSA</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>MANZANO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CORREA</t>
-  </si>
-  <si>
-    <t>CARLOS DAVID</t>
+    <t>RAFAEL FELIPE</t>
+  </si>
+  <si>
+    <t>ANGEL YAMIL</t>
+  </si>
+  <si>
+    <t>JUAN ALBERTO</t>
+  </si>
+  <si>
+    <t>JOSE GUADALUPE</t>
+  </si>
+  <si>
+    <t>YAELIS</t>
+  </si>
+  <si>
+    <t>HUGO ISAI</t>
+  </si>
+  <si>
+    <t>MARY CELESTE</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>KEVIN IVAN</t>
+  </si>
+  <si>
+    <t>DANNAE ADALID</t>
+  </si>
+  <si>
+    <t>LUIS AARON</t>
+  </si>
+  <si>
+    <t>OMAR DAVID</t>
+  </si>
+  <si>
+    <t>JUAN SEBASTIAN</t>
+  </si>
+  <si>
+    <t>JUAN YAHEL</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>JAZIEL</t>
   </si>
   <si>
     <t>IAN</t>
   </si>
   <si>
-    <t>HUGO ISAI</t>
-  </si>
-  <si>
-    <t>ROMINA GISELLE</t>
+    <t>YAEL ISSAI</t>
+  </si>
+  <si>
+    <t>LLUVIA ITZEL</t>
+  </si>
+  <si>
+    <t>DENISSE</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>ILSE JIMENA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>MELANY</t>
   </si>
   <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>DIANA ARLET</t>
+    <t>ANIELA SAMANTA</t>
+  </si>
+  <si>
+    <t>MARGARITA</t>
+  </si>
+  <si>
+    <t>DANIA LIZETH</t>
   </si>
   <si>
     <t>MARITZA</t>
   </si>
   <si>
-    <t>ESTRELLA ESMERALDA</t>
-  </si>
-  <si>
-    <t>ESTRELLA RUBI</t>
-  </si>
-  <si>
-    <t>LEONARDO GABRIEL</t>
+    <t>ANGEL URIEL</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>DORIAN ALEXANDER</t>
+  </si>
+  <si>
+    <t>JOSELYN</t>
   </si>
   <si>
     <t>VICTOR JESUS</t>
   </si>
   <si>
     <t>JONATHAN ISAI</t>
-  </si>
-  <si>
-    <t>OMAR DAVID</t>
-  </si>
-  <si>
-    <t>JUAN SEBASTIAN</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
-  </si>
-  <si>
-    <t>JAZIEL</t>
-  </si>
-  <si>
-    <t>YAELIS</t>
-  </si>
-  <si>
-    <t>LLUVIA ITZEL</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>XIMENA ANALY</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>JANETH</t>
-  </si>
-  <si>
-    <t>ILSE JIMENA</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MARGARITA</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>TATIANA</t>
-  </si>
-  <si>
-    <t>DANIA LIZETH</t>
-  </si>
-  <si>
-    <t>KENIA PAOLA</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>MARYGELLI</t>
-  </si>
-  <si>
-    <t>ANGEL URIEL</t>
-  </si>
-  <si>
-    <t>KAREN AMERICA</t>
-  </si>
-  <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>MAGALY</t>
-  </si>
-  <si>
-    <t>LEYLA SARAI</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>DORIAN ALEXANDER</t>
-  </si>
-  <si>
-    <t>KENYA MARIANA</t>
-  </si>
-  <si>
-    <t>SALMA JANET</t>
-  </si>
-  <si>
-    <t>ELIUD EDUARDO</t>
-  </si>
-  <si>
-    <t>KAORY AYELEN</t>
   </si>
 </sst>
 </file>
@@ -1337,16 +1274,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>37.04</v>
+        <v>48.15</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1389,16 +1326,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>61.76</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1424,7 +1361,7 @@
         <v>91.18000000000001</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1441,13 +1378,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>57.5</v>
+        <v>75</v>
       </c>
       <c r="H6">
         <v>6.5</v>
@@ -1487,16 +1424,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G8">
-        <v>46.15</v>
+        <v>74.36</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1513,16 +1450,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G9">
-        <v>36.67</v>
+        <v>66.67</v>
       </c>
       <c r="H9">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1469,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1564,16 +1501,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920018</v>
+        <v>23330051920006</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1587,22 +1524,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920043</v>
+        <v>23330051920017</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1610,22 +1547,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920052</v>
+        <v>23330051920025</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1633,22 +1570,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920095</v>
+        <v>23330051920030</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1656,22 +1593,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920105</v>
+        <v>23330051920049</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1679,22 +1616,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920118</v>
+        <v>23330051920052</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1702,22 +1639,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920123</v>
+        <v>23330051920351</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1725,22 +1662,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920139</v>
+        <v>23330051920097</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1748,16 +1685,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920155</v>
+        <v>23330051920162</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1771,16 +1708,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920154</v>
+        <v>23330051920175</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1794,16 +1731,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920166</v>
+        <v>23330051920313</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1817,62 +1754,62 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920169</v>
+        <v>23330051920005</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920171</v>
+        <v>23330051920008</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920005</v>
+        <v>23330051920015</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1886,16 +1823,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920008</v>
+        <v>23330051920021</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1909,16 +1846,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920009</v>
+        <v>23330051920020</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1932,16 +1869,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920021</v>
+        <v>23330051920022</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1955,22 +1892,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920020</v>
+        <v>23330051920028</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1984,10 +1921,10 @@
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -2001,16 +1938,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920037</v>
+        <v>23330051920032</v>
       </c>
       <c r="B21" t="s">
         <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -2030,10 +1967,10 @@
         <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -2047,22 +1984,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920049</v>
+        <v>23330051920043</v>
       </c>
       <c r="B23" t="s">
         <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -2070,22 +2007,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920246</v>
+        <v>23330051920046</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -2093,16 +2030,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920065</v>
+        <v>23330051920246</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2116,16 +2053,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920067</v>
+        <v>23330051920065</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2142,13 +2079,13 @@
         <v>23330051920072</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D27" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2162,16 +2099,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920077</v>
+        <v>23330051920079</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2185,16 +2122,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920079</v>
+        <v>23330051920084</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2208,16 +2145,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920082</v>
+        <v>23330051920104</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2231,16 +2168,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920083</v>
+        <v>23330051920105</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2254,16 +2191,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920086</v>
+        <v>23330051920261</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D32" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2277,16 +2214,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920084</v>
+        <v>23330051920112</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2300,22 +2237,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920091</v>
+        <v>23330051920133</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2323,22 +2260,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920104</v>
+        <v>23330051920139</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2346,22 +2283,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920112</v>
+        <v>23330051920315</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2369,22 +2306,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920121</v>
+        <v>23330051920157</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2392,22 +2329,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>23330051920130</v>
+        <v>23330051920158</v>
       </c>
       <c r="B38" t="s">
         <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2415,22 +2352,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>23330051920133</v>
+        <v>23330051920161</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C39" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="D39" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2438,22 +2375,22 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>23330051920134</v>
+        <v>23330051920169</v>
       </c>
       <c r="B40" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="D40" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2461,323 +2398,24 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>23330051920255</v>
+        <v>23330051920171</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C41" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>23330051920141</v>
-      </c>
-      <c r="B42" t="s">
-        <v>44</v>
-      </c>
-      <c r="C42" t="s">
-        <v>87</v>
-      </c>
-      <c r="D42" t="s">
-        <v>132</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>15</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>23330051920315</v>
-      </c>
-      <c r="B43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" t="s">
-        <v>133</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>15</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>23330051920142</v>
-      </c>
-      <c r="B44" t="s">
-        <v>33</v>
-      </c>
-      <c r="C44" t="s">
-        <v>46</v>
-      </c>
-      <c r="D44" t="s">
-        <v>134</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>15</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>23330051920144</v>
-      </c>
-      <c r="B45" t="s">
-        <v>56</v>
-      </c>
-      <c r="C45" t="s">
-        <v>56</v>
-      </c>
-      <c r="D45" t="s">
-        <v>135</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>15</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>23330051920145</v>
-      </c>
-      <c r="B46" t="s">
-        <v>57</v>
-      </c>
-      <c r="C46" t="s">
-        <v>39</v>
-      </c>
-      <c r="D46" t="s">
-        <v>136</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>15</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>23330051920146</v>
-      </c>
-      <c r="B47" t="s">
-        <v>39</v>
-      </c>
-      <c r="C47" t="s">
-        <v>89</v>
-      </c>
-      <c r="D47" t="s">
-        <v>137</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>15</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>23330051920150</v>
-      </c>
-      <c r="B48" t="s">
-        <v>58</v>
-      </c>
-      <c r="C48" t="s">
-        <v>76</v>
-      </c>
-      <c r="D48" t="s">
-        <v>138</v>
-      </c>
-      <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>15</v>
-      </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>23330051920157</v>
-      </c>
-      <c r="B49" t="s">
-        <v>40</v>
-      </c>
-      <c r="C49" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49" t="s">
-        <v>139</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>16</v>
-      </c>
-      <c r="G49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>23330051920158</v>
-      </c>
-      <c r="B50" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" t="s">
-        <v>39</v>
-      </c>
-      <c r="D50" t="s">
-        <v>140</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>16</v>
-      </c>
-      <c r="G50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>23330051920165</v>
-      </c>
-      <c r="B51" t="s">
-        <v>59</v>
-      </c>
-      <c r="C51" t="s">
-        <v>89</v>
-      </c>
-      <c r="D51" t="s">
-        <v>141</v>
-      </c>
-      <c r="E51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>16</v>
-      </c>
-      <c r="G51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52">
-        <v>23330051920167</v>
-      </c>
-      <c r="B52" t="s">
-        <v>60</v>
-      </c>
-      <c r="C52" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" t="s">
-        <v>142</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>16</v>
-      </c>
-      <c r="G52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>23330051920354</v>
-      </c>
-      <c r="B53" t="s">
-        <v>33</v>
-      </c>
-      <c r="C53" t="s">
-        <v>90</v>
-      </c>
-      <c r="D53" t="s">
-        <v>143</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>16</v>
-      </c>
-      <c r="G53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54">
-        <v>23330051920170</v>
-      </c>
-      <c r="B54" t="s">
-        <v>61</v>
-      </c>
-      <c r="C54" t="s">
-        <v>91</v>
-      </c>
-      <c r="D54" t="s">
-        <v>144</v>
-      </c>
-      <c r="E54" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>16</v>
-      </c>
-      <c r="G54">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="121">
   <si>
     <t>Mat</t>
   </si>
@@ -181,9 +181,6 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
@@ -259,9 +256,6 @@
     <t>PAZ</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>MANZANO</t>
   </si>
   <si>
@@ -368,9 +362,6 @@
   </si>
   <si>
     <t>DANIA LIZETH</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
   </si>
   <si>
     <t>ANGEL URIEL</t>
@@ -1424,13 +1415,13 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>74.36</v>
+        <v>76.92</v>
       </c>
       <c r="H8">
         <v>6.5</v>
@@ -1469,7 +1460,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1507,10 +1498,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1530,10 +1521,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1553,10 +1544,10 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1576,10 +1567,10 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1599,10 +1590,10 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1622,10 +1613,10 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1648,7 +1639,7 @@
         <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1671,7 +1662,7 @@
         <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1694,7 +1685,7 @@
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1714,10 +1705,10 @@
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1740,7 +1731,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1760,10 +1751,10 @@
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1786,7 +1777,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1809,7 +1800,7 @@
         <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1829,10 +1820,10 @@
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1852,10 +1843,10 @@
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1875,10 +1866,10 @@
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1901,7 +1892,7 @@
         <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1921,10 +1912,10 @@
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1944,10 +1935,10 @@
         <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1967,10 +1958,10 @@
         <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1990,10 +1981,10 @@
         <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -2013,10 +2004,10 @@
         <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -2036,10 +2027,10 @@
         <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2059,10 +2050,10 @@
         <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2082,10 +2073,10 @@
         <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2105,10 +2096,10 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2131,7 +2122,7 @@
         <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2151,10 +2142,10 @@
         <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2174,10 +2165,10 @@
         <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2197,10 +2188,10 @@
         <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2220,10 +2211,10 @@
         <v>52</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D33" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2243,10 +2234,10 @@
         <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2260,16 +2251,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920139</v>
+        <v>23330051920315</v>
       </c>
       <c r="B35" t="s">
         <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2283,22 +2274,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920315</v>
+        <v>23330051920157</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2306,16 +2297,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920157</v>
+        <v>23330051920158</v>
       </c>
       <c r="B37" t="s">
         <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2329,16 +2320,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>23330051920158</v>
+        <v>23330051920161</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2352,16 +2343,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>23330051920161</v>
+        <v>23330051920169</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2375,16 +2366,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>23330051920169</v>
+        <v>23330051920171</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2393,29 +2384,6 @@
         <v>16</v>
       </c>
       <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>23330051920171</v>
-      </c>
-      <c r="B41" t="s">
-        <v>47</v>
-      </c>
-      <c r="C41" t="s">
-        <v>40</v>
-      </c>
-      <c r="D41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>16</v>
-      </c>
-      <c r="G41">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
@@ -907,16 +907,22 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="G7">
+        <v>95</v>
+      </c>
+      <c r="H7">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1148,16 +1154,22 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="G7">
+        <v>95</v>
+      </c>
+      <c r="H7">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1389,16 +1401,22 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="G7">
+        <v>95</v>
+      </c>
+      <c r="H7">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
@@ -1286,7 +1286,7 @@
         <v>48.15</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1312,7 +1312,7 @@
         <v>41.67</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1338,7 +1338,7 @@
         <v>67.65000000000001</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1364,7 +1364,7 @@
         <v>91.18000000000001</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1390,7 +1390,7 @@
         <v>75</v>
       </c>
       <c r="H6">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1442,7 +1442,7 @@
         <v>76.92</v>
       </c>
       <c r="H8">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1468,7 +1468,7 @@
         <v>66.67</v>
       </c>
       <c r="H9">
-        <v>6.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20231.xlsx
@@ -1286,7 +1286,7 @@
         <v>48.15</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1312,7 +1312,7 @@
         <v>41.67</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1338,7 +1338,7 @@
         <v>67.65000000000001</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1364,7 +1364,7 @@
         <v>91.18000000000001</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1390,7 +1390,7 @@
         <v>75</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1442,7 +1442,7 @@
         <v>76.92</v>
       </c>
       <c r="H8">
-        <v>8.800000000000001</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1468,7 +1468,7 @@
         <v>66.67</v>
       </c>
       <c r="H9">
-        <v>8.300000000000001</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
